--- a/Outputs_primates/AllGenes_Potential_CPDs.xlsx
+++ b/Outputs_primates/AllGenes_Potential_CPDs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uofh-my.sharepoint.com/personal/miadesin_cougarnet_uh_edu/Documents/Documents/Ricardo_lab/GitHub/kondrashov/Outputs_primates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="156" documentId="13_ncr:1_{8A2AFB6C-B6BE-D242-8FA1-EF65A1680E88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DBD0D20B-0FCC-4C18-8F22-AD19154620D6}"/>
+  <xr:revisionPtr revIDLastSave="205" documentId="13_ncr:1_{8A2AFB6C-B6BE-D242-8FA1-EF65A1680E88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4D3ACBE-0207-4BDC-BC90-25D80907F3D5}"/>
   <bookViews>
-    <workbookView xWindow="7416" yWindow="0" windowWidth="15720" windowHeight="12336" xr2:uid="{BC6F7999-E049-F441-AF63-5F5D062E3B8F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BC6F7999-E049-F441-AF63-5F5D062E3B8F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="268">
   <si>
     <t>gene</t>
   </si>
@@ -815,20 +815,41 @@
     <t>NP_055610.1</t>
   </si>
   <si>
-    <t>orthologs</t>
-  </si>
-  <si>
     <t>Aln</t>
   </si>
   <si>
     <t>species</t>
+  </si>
+  <si>
+    <t>Unlike other CPDs, the human species only has the 'wild', all other species have the 'mut'      lollll!</t>
+  </si>
+  <si>
+    <t>Hannah's</t>
+  </si>
+  <si>
+    <t>at site 491</t>
+  </si>
+  <si>
+    <t>Nil</t>
+  </si>
+  <si>
+    <t>Looks like a CPD, except that flanking region contains one gap, but gap is consistent across alignment</t>
+  </si>
+  <si>
+    <t>This is valid, although Hannah did not detect it among her 2 CPDs. Maybe I filter the alignment to exclude the gaps?</t>
+  </si>
+  <si>
+    <t>valid CPD</t>
+  </si>
+  <si>
+    <t>Hannah detected 5 CPDs! LDLR Alignment should be filtered; there are multiple gaps in-between</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -852,25 +873,46 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
       <color theme="7"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="12"/>
       <color rgb="FF00B0F0"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="7"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -900,16 +942,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1269,7 +1315,7 @@
         <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>3</v>
@@ -1281,10 +1327,10 @@
         <v>5</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -1312,9 +1358,6 @@
       <c r="H2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="1">
-        <v>34</v>
-      </c>
       <c r="J2" s="3"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -2097,7 +2140,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>64</v>
       </c>
@@ -2123,33 +2166,36 @@
         <v>24</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="1" t="s">
+    <row r="34" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="D34" s="1">
+      <c r="D34" s="5">
         <v>969</v>
       </c>
-      <c r="E34" s="1">
+      <c r="E34" s="5">
         <v>1102</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="F34" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G34" s="1" t="s">
+      <c r="G34" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H34" s="1" t="s">
+      <c r="H34" s="5" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I34" s="5" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>67</v>
       </c>
@@ -2175,33 +2221,33 @@
         <v>69</v>
       </c>
     </row>
-    <row r="36" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="5" t="s">
+    <row r="36" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="C36" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="D36" s="5">
+      <c r="D36" s="4">
         <v>438</v>
       </c>
-      <c r="E36" s="5">
+      <c r="E36" s="4">
         <v>475</v>
       </c>
-      <c r="F36" s="5" t="s">
+      <c r="F36" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="G36" s="5" t="s">
+      <c r="G36" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H36" s="5" t="s">
+      <c r="H36" s="4" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="37" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>73</v>
       </c>
@@ -2227,7 +2273,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="38" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>73</v>
       </c>
@@ -2253,7 +2299,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>76</v>
       </c>
@@ -2279,7 +2325,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>76</v>
       </c>
@@ -2305,7 +2351,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="41" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>79</v>
       </c>
@@ -2331,33 +2377,33 @@
         <v>14</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" s="1" t="s">
+    <row r="42" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B42" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="D42" s="1">
+      <c r="D42" s="5">
         <v>13</v>
       </c>
-      <c r="E42" s="1">
+      <c r="E42" s="5">
         <v>128</v>
       </c>
-      <c r="F42" s="1" t="s">
+      <c r="F42" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G42" s="1" t="s">
+      <c r="G42" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="H42" s="1" t="s">
+      <c r="H42" s="5" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="43" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
         <v>81</v>
       </c>
@@ -2383,7 +2429,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>85</v>
       </c>
@@ -2409,7 +2455,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="45" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>87</v>
       </c>
@@ -2435,7 +2481,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>87</v>
       </c>
@@ -2461,7 +2507,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="47" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>90</v>
       </c>
@@ -2487,7 +2533,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>92</v>
       </c>
@@ -2666,81 +2712,81 @@
         <v>56</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A55" s="1" t="s">
+    <row r="55" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B55" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="D55" s="1">
+      <c r="D55" s="5">
         <v>2038</v>
       </c>
-      <c r="E55" s="1">
+      <c r="E55" s="5">
         <v>2055</v>
       </c>
-      <c r="F55" s="1" t="s">
+      <c r="F55" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="G55" s="1" t="s">
+      <c r="G55" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="H55" s="1" t="s">
+      <c r="H55" s="5" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A56" s="1" t="s">
+    <row r="56" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B56" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C56" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="D56" s="1">
+      <c r="D56" s="5">
         <v>2157</v>
       </c>
-      <c r="E56" s="1">
+      <c r="E56" s="5">
         <v>2174</v>
       </c>
-      <c r="F56" s="1" t="s">
+      <c r="F56" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="G56" s="1" t="s">
+      <c r="G56" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="H56" s="1" t="s">
+      <c r="H56" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A57" s="1" t="s">
+    <row r="57" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="B57" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C57" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="D57" s="1">
+      <c r="D57" s="5">
         <v>75</v>
       </c>
-      <c r="E57" s="1">
+      <c r="E57" s="5">
         <v>75</v>
       </c>
-      <c r="F57" s="1" t="s">
+      <c r="F57" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G57" s="1" t="s">
+      <c r="G57" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H57" s="1" t="s">
+      <c r="H57" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -2923,7 +2969,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="65" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
         <v>121</v>
       </c>
@@ -2949,7 +2995,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="66" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
         <v>121</v>
       </c>
@@ -2975,189 +3021,198 @@
         <v>124</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A67" s="1" t="s">
+    <row r="67" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B67" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="C67" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="D67" s="1">
+      <c r="D67" s="9">
         <v>223</v>
       </c>
-      <c r="E67" s="1">
+      <c r="E67" s="9">
         <v>249</v>
       </c>
-      <c r="F67" s="1" t="s">
+      <c r="F67" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="G67" s="1" t="s">
+      <c r="G67" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="H67" s="1" t="s">
+      <c r="H67" s="9" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A68" s="1" t="s">
+      <c r="I67" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="J67" s="9" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="B68" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="C68" s="1" t="s">
+      <c r="C68" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="D68" s="1">
+      <c r="D68" s="7">
         <v>502</v>
       </c>
-      <c r="E68" s="1">
+      <c r="E68" s="7">
         <v>506</v>
       </c>
-      <c r="F68" s="1" t="s">
+      <c r="F68" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="G68" s="1" t="s">
+      <c r="G68" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="H68" s="1" t="s">
+      <c r="H68" s="7" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="69" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="5" t="s">
+      <c r="J68" s="7" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="B69" s="5" t="s">
+      <c r="B69" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="C69" s="5" t="s">
+      <c r="C69" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="D69" s="5">
+      <c r="D69" s="6">
         <v>535</v>
       </c>
-      <c r="E69" s="5">
+      <c r="E69" s="6">
         <v>539</v>
       </c>
-      <c r="F69" s="5" t="s">
+      <c r="F69" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G69" s="5" t="s">
+      <c r="G69" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H69" s="5" t="s">
+      <c r="H69" s="6" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A70" s="1" t="s">
+    <row r="70" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="B70" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="C70" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="D70" s="1">
+      <c r="D70" s="5">
         <v>227</v>
       </c>
-      <c r="E70" s="1">
+      <c r="E70" s="5">
         <v>229</v>
       </c>
-      <c r="F70" s="1" t="s">
+      <c r="F70" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="G70" s="1" t="s">
+      <c r="G70" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="H70" s="1" t="s">
+      <c r="H70" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A71" s="1" t="s">
+    <row r="71" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="B71" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="C71" s="1" t="s">
+      <c r="C71" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="D71" s="1">
+      <c r="D71" s="5">
         <v>351</v>
       </c>
-      <c r="E71" s="1">
+      <c r="E71" s="5">
         <v>353</v>
       </c>
-      <c r="F71" s="1" t="s">
+      <c r="F71" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="G71" s="1" t="s">
+      <c r="G71" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="H71" s="1" t="s">
+      <c r="H71" s="5" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A72" s="1" t="s">
+    <row r="72" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="B72" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="C72" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="D72" s="1">
+      <c r="D72" s="5">
         <v>350</v>
       </c>
-      <c r="E72" s="1">
+      <c r="E72" s="5">
         <v>352</v>
       </c>
-      <c r="F72" s="1" t="s">
+      <c r="F72" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G72" s="1" t="s">
+      <c r="G72" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="H72" s="1" t="s">
+      <c r="H72" s="5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A73" s="1" t="s">
+    <row r="73" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="B73" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="C73" s="1" t="s">
+      <c r="C73" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="D73" s="1">
+      <c r="D73" s="5">
         <v>416</v>
       </c>
-      <c r="E73" s="1">
+      <c r="E73" s="5">
         <v>419</v>
       </c>
-      <c r="F73" s="1" t="s">
+      <c r="F73" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G73" s="1" t="s">
+      <c r="G73" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="H73" s="1" t="s">
+      <c r="H73" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>128</v>
       </c>
@@ -3183,7 +3238,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>128</v>
       </c>
@@ -3209,33 +3264,33 @@
         <v>42</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A76" s="1" t="s">
+    <row r="76" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="B76" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="C76" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="D76" s="1">
+      <c r="D76" s="5">
         <v>351</v>
       </c>
-      <c r="E76" s="1">
+      <c r="E76" s="5">
         <v>353</v>
       </c>
-      <c r="F76" s="1" t="s">
+      <c r="F76" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="G76" s="1" t="s">
+      <c r="G76" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="H76" s="1" t="s">
+      <c r="H76" s="5" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="77" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
         <v>128</v>
       </c>
@@ -3261,7 +3316,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>130</v>
       </c>
@@ -3287,7 +3342,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="79" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
         <v>130</v>
       </c>
@@ -3313,7 +3368,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>133</v>
       </c>
@@ -3339,7 +3394,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>135</v>
       </c>
@@ -3365,7 +3420,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>137</v>
       </c>
@@ -3391,7 +3446,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="83" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
         <v>137</v>
       </c>
@@ -3417,7 +3472,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="84" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
         <v>137</v>
       </c>
@@ -3443,7 +3498,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="85" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="s">
         <v>137</v>
       </c>
@@ -3469,7 +3524,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="86" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
         <v>137</v>
       </c>
@@ -3495,7 +3550,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="87" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
         <v>144</v>
       </c>
@@ -3520,8 +3575,11 @@
       <c r="H87" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="88" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="J87" s="10" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A88" s="4" t="s">
         <v>144</v>
       </c>
@@ -3547,7 +3605,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="89" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
         <v>144</v>
       </c>
@@ -3573,33 +3631,36 @@
         <v>42</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A90" s="1" t="s">
+    <row r="90" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="B90" s="1" t="s">
+      <c r="B90" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="C90" s="1" t="s">
+      <c r="C90" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="D90" s="1">
+      <c r="D90" s="6">
         <v>88</v>
       </c>
-      <c r="E90" s="1">
+      <c r="E90" s="6">
         <v>125</v>
       </c>
-      <c r="F90" s="1" t="s">
+      <c r="F90" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G90" s="1" t="s">
+      <c r="G90" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="H90" s="1" t="s">
+      <c r="H90" s="6" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="91" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="I90" s="6" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
         <v>144</v>
       </c>
@@ -3625,7 +3686,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="92" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="s">
         <v>147</v>
       </c>
@@ -3651,7 +3712,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
         <v>147</v>
       </c>
@@ -3677,7 +3738,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="94" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
         <v>147</v>
       </c>
@@ -3703,7 +3764,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
         <v>152</v>
       </c>
@@ -3729,7 +3790,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
         <v>152</v>
       </c>
@@ -3807,55 +3868,55 @@
         <v>132</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A99" s="1" t="s">
+    <row r="99" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="B99" s="1" t="s">
+      <c r="B99" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="C99" s="1" t="s">
+      <c r="C99" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="D99" s="1">
+      <c r="D99" s="5">
         <v>176</v>
       </c>
-      <c r="E99" s="1">
+      <c r="E99" s="5">
         <v>197</v>
       </c>
-      <c r="F99" s="1" t="s">
+      <c r="F99" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G99" s="1" t="s">
+      <c r="G99" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H99" s="1" t="s">
+      <c r="H99" s="5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A100" s="1" t="s">
+    <row r="100" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="B100" s="1" t="s">
+      <c r="B100" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="C100" s="1" t="s">
+      <c r="C100" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="D100" s="1">
+      <c r="D100" s="5">
         <v>413</v>
       </c>
-      <c r="E100" s="1">
+      <c r="E100" s="5">
         <v>434</v>
       </c>
-      <c r="F100" s="1" t="s">
+      <c r="F100" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G100" s="1" t="s">
+      <c r="G100" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="H100" s="1" t="s">
+      <c r="H100" s="5" t="s">
         <v>60</v>
       </c>
     </row>
@@ -4171,137 +4232,137 @@
         <v>186</v>
       </c>
     </row>
-    <row r="113" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="5" t="s">
+    <row r="113" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="B113" s="5" t="s">
+      <c r="B113" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="C113" s="5" t="s">
+      <c r="C113" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="D113" s="5">
+      <c r="D113" s="6">
         <v>142</v>
       </c>
-      <c r="E113" s="5">
+      <c r="E113" s="6">
         <v>142</v>
       </c>
-      <c r="F113" s="5" t="s">
+      <c r="F113" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="G113" s="5" t="s">
+      <c r="G113" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="H113" s="5" t="s">
+      <c r="H113" s="6" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A114" s="1" t="s">
+    <row r="114" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="B114" s="1" t="s">
+      <c r="B114" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="C114" s="1" t="s">
+      <c r="C114" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="D114" s="1">
+      <c r="D114" s="5">
         <v>127</v>
       </c>
-      <c r="E114" s="1">
+      <c r="E114" s="5">
         <v>127</v>
       </c>
-      <c r="F114" s="1" t="s">
+      <c r="F114" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="G114" s="1" t="s">
+      <c r="G114" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H114" s="1" t="s">
+      <c r="H114" s="5" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A115" s="1" t="s">
+    <row r="115" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="B115" s="1" t="s">
+      <c r="B115" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="C115" s="1" t="s">
+      <c r="C115" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="D115" s="1">
+      <c r="D115" s="5">
         <v>82</v>
       </c>
-      <c r="E115" s="1">
+      <c r="E115" s="5">
         <v>82</v>
       </c>
-      <c r="F115" s="1" t="s">
+      <c r="F115" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="G115" s="1" t="s">
+      <c r="G115" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="H115" s="1" t="s">
+      <c r="H115" s="5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A116" s="1" t="s">
+    <row r="116" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="B116" s="1" t="s">
+      <c r="B116" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="C116" s="1" t="s">
+      <c r="C116" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="D116" s="1">
+      <c r="D116" s="5">
         <v>77</v>
       </c>
-      <c r="E116" s="1">
+      <c r="E116" s="5">
         <v>77</v>
       </c>
-      <c r="F116" s="1" t="s">
+      <c r="F116" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G116" s="1" t="s">
+      <c r="G116" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="H116" s="1" t="s">
+      <c r="H116" s="5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A117" s="1" t="s">
+    <row r="117" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="B117" s="1" t="s">
+      <c r="B117" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="C117" s="1" t="s">
+      <c r="C117" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="D117" s="1">
+      <c r="D117" s="5">
         <v>126</v>
       </c>
-      <c r="E117" s="1">
+      <c r="E117" s="5">
         <v>126</v>
       </c>
-      <c r="F117" s="1" t="s">
+      <c r="F117" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="G117" s="1" t="s">
+      <c r="G117" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="H117" s="1" t="s">
+      <c r="H117" s="5" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
         <v>189</v>
       </c>
@@ -4327,7 +4388,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="119" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A119" s="4" t="s">
         <v>191</v>
       </c>
@@ -4353,7 +4414,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="120" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A120" s="4" t="s">
         <v>191</v>
       </c>
@@ -4379,7 +4440,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="121" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A121" s="4" t="s">
         <v>191</v>
       </c>
@@ -4405,7 +4466,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="122" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A122" s="4" t="s">
         <v>191</v>
       </c>
@@ -4431,7 +4492,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="123" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A123" s="4" t="s">
         <v>191</v>
       </c>
@@ -4457,7 +4518,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="124" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A124" s="4" t="s">
         <v>191</v>
       </c>
@@ -4483,7 +4544,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="125" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A125" s="4" t="s">
         <v>193</v>
       </c>
@@ -4509,33 +4570,36 @@
         <v>22</v>
       </c>
     </row>
-    <row r="126" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="6" t="s">
+    <row r="126" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A126" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="B126" s="6" t="s">
+      <c r="B126" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="C126" s="6" t="s">
+      <c r="C126" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="D126" s="6">
+      <c r="D126" s="8">
         <v>341</v>
       </c>
-      <c r="E126" s="6">
+      <c r="E126" s="8">
         <v>523</v>
       </c>
-      <c r="F126" s="6" t="s">
+      <c r="F126" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G126" s="6" t="s">
+      <c r="G126" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="H126" s="6" t="s">
+      <c r="H126" s="8" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J126" s="8" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
         <v>197</v>
       </c>

--- a/Outputs_primates/AllGenes_Potential_CPDs.xlsx
+++ b/Outputs_primates/AllGenes_Potential_CPDs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uofh-my.sharepoint.com/personal/miadesin_cougarnet_uh_edu/Documents/Documents/Ricardo_lab/GitHub/kondrashov/Outputs_primates/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adesinamary/Downloads/kondrashov/Outputs_primates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="205" documentId="13_ncr:1_{8A2AFB6C-B6BE-D242-8FA1-EF65A1680E88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4D3ACBE-0207-4BDC-BC90-25D80907F3D5}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7115085-B8C9-E948-9630-677186C5056D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BC6F7999-E049-F441-AF63-5F5D062E3B8F}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="23260" windowHeight="12460" xr2:uid="{BC6F7999-E049-F441-AF63-5F5D062E3B8F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="276">
   <si>
     <t>gene</t>
   </si>
@@ -843,13 +843,37 @@
   </si>
   <si>
     <t>Hannah detected 5 CPDs! LDLR Alignment should be filtered; there are multiple gaps in-between</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACADVL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NM_000018.4 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> V</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> M</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ['M']</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NP_000009.1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> S</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ['S']</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -900,6 +924,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -942,7 +972,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -954,8 +984,10 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1290,18 +1322,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81CD1290-D98E-6145-998E-728A92BEC841}">
-  <dimension ref="A1:J127"/>
-  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:J129"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.19921875" style="1"/>
-    <col min="2" max="2" width="18.796875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1640625" style="1"/>
+    <col min="2" max="2" width="18.83203125" style="1" customWidth="1"/>
     <col min="3" max="3" width="17" style="1" customWidth="1"/>
-    <col min="4" max="9" width="11.19921875" style="1"/>
-    <col min="10" max="10" width="55.296875" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="11.19921875" style="1"/>
+    <col min="4" max="9" width="11.1640625" style="1"/>
+    <col min="10" max="10" width="55.33203125" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="11.1640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1333,7 +1365,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -1360,7 +1392,7 @@
       </c>
       <c r="J2" s="3"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -1386,7 +1418,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -1412,7 +1444,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -1438,189 +1470,189 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="D6" s="12">
+        <v>174</v>
+      </c>
+      <c r="E6" s="12">
+        <v>221</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B7" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="D7" s="12">
+        <v>219</v>
+      </c>
+      <c r="E7" s="12">
+        <v>266</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C8" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D8" s="5">
         <v>286</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E8" s="5">
         <v>333</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F8" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G8" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H8" s="5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+    <row r="9" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B9" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C9" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D9" s="4">
         <v>1</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E9" s="4">
         <v>115</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F9" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H9" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
+    <row r="10" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B10" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C10" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D10" s="4">
         <v>1</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E10" s="4">
         <v>115</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F10" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H10" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
+    <row r="11" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B11" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C11" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D11" s="4">
         <v>15</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E11" s="4">
         <v>54</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F11" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G11" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H11" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
+    <row r="12" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B12" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C12" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D12" s="4">
         <v>17</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E12" s="4">
         <v>56</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G12" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H12" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="D11" s="1">
-        <v>156</v>
-      </c>
-      <c r="E11" s="1">
-        <v>260</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="D12" s="4">
-        <v>260</v>
-      </c>
-      <c r="E12" s="4">
-        <v>364</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>31</v>
       </c>
@@ -1631,10 +1663,10 @@
         <v>204</v>
       </c>
       <c r="D13" s="1">
-        <v>82</v>
+        <v>156</v>
       </c>
       <c r="E13" s="1">
-        <v>105</v>
+        <v>260</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>33</v>
@@ -1646,137 +1678,137 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="D14" s="4">
+        <v>260</v>
+      </c>
+      <c r="E14" s="4">
+        <v>364</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D15" s="1">
+        <v>82</v>
+      </c>
+      <c r="E15" s="1">
+        <v>105</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B16" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C16" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D16" s="4">
         <v>383</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E16" s="4">
         <v>397</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F16" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G16" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="H16" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
+    <row r="17" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B17" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C17" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D17" s="4">
         <v>21</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E17" s="4">
         <v>184</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F17" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G17" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="H17" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
+    <row r="18" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B18" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C18" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D18" s="4">
         <v>1</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E18" s="4">
         <v>164</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F18" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G18" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="H18" s="4" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="D17" s="1">
-        <v>2378</v>
-      </c>
-      <c r="E17" s="1">
-        <v>3867</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="D18" s="4">
-        <v>1155</v>
-      </c>
-      <c r="E18" s="4">
-        <v>2307</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>48</v>
       </c>
@@ -1787,126 +1819,126 @@
         <v>207</v>
       </c>
       <c r="D19" s="1">
+        <v>2378</v>
+      </c>
+      <c r="E19" s="1">
+        <v>3867</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="D20" s="4">
+        <v>1155</v>
+      </c>
+      <c r="E20" s="4">
+        <v>2307</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="D21" s="1">
         <v>1459</v>
       </c>
-      <c r="E19" s="1">
+      <c r="E21" s="1">
         <v>2851</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="F21" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="G21" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="H21" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B22" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C22" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D22" s="1">
         <v>2465</v>
       </c>
-      <c r="E20" s="1">
+      <c r="E22" s="1">
         <v>3954</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F22" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G20" s="1" t="s">
+      <c r="G22" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="H22" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="21" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
+    <row r="23" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B23" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C23" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D23" s="4">
         <v>51</v>
       </c>
-      <c r="E21" s="4">
+      <c r="E23" s="4">
         <v>94</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="F23" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="G23" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="H21" s="4" t="s">
+      <c r="H23" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="22" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="D22" s="4">
-        <v>82</v>
-      </c>
-      <c r="E22" s="4">
-        <v>128</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="D23" s="1">
-        <v>82</v>
-      </c>
-      <c r="E23" s="1">
-        <v>128</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>53</v>
       </c>
@@ -1917,22 +1949,22 @@
         <v>208</v>
       </c>
       <c r="D24" s="4">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E24" s="4">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>53</v>
       </c>
@@ -1943,126 +1975,126 @@
         <v>208</v>
       </c>
       <c r="D25" s="1">
+        <v>82</v>
+      </c>
+      <c r="E25" s="1">
+        <v>128</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="D26" s="4">
+        <v>85</v>
+      </c>
+      <c r="E26" s="4">
+        <v>138</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D27" s="1">
         <v>93</v>
       </c>
-      <c r="E25" s="1">
+      <c r="E27" s="1">
         <v>155</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="F27" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G25" s="1" t="s">
+      <c r="G27" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H25" s="1" t="s">
+      <c r="H27" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B28" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C28" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="D26" s="1">
+      <c r="D28" s="1">
         <v>295</v>
       </c>
-      <c r="E26" s="1">
+      <c r="E28" s="1">
         <v>372</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="F28" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G26" s="1" t="s">
+      <c r="G28" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H26" s="1" t="s">
+      <c r="H28" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="4" t="s">
+    <row r="29" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B29" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C29" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="D27" s="4">
+      <c r="D29" s="4">
         <v>97</v>
       </c>
-      <c r="E27" s="4">
+      <c r="E29" s="4">
         <v>150</v>
       </c>
-      <c r="F27" s="4" t="s">
+      <c r="F29" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G27" s="4" t="s">
+      <c r="G29" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H27" s="4" t="s">
+      <c r="H29" s="4" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="28" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="D28" s="4">
-        <v>85</v>
-      </c>
-      <c r="E28" s="4">
-        <v>138</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H28" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="D29" s="1">
-        <v>152</v>
-      </c>
-      <c r="E29" s="1">
-        <v>205</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>58</v>
       </c>
@@ -2073,519 +2105,519 @@
         <v>209</v>
       </c>
       <c r="D30" s="4">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="E30" s="4">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>62</v>
+        <v>11</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D31" s="1">
-        <v>113</v>
+        <v>152</v>
       </c>
       <c r="E31" s="1">
-        <v>158</v>
+        <v>205</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D32" s="4">
-        <v>146</v>
+        <v>95</v>
       </c>
       <c r="E32" s="4">
-        <v>191</v>
+        <v>148</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>8</v>
       </c>
       <c r="G32" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A33" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D33" s="1">
+        <v>113</v>
+      </c>
+      <c r="E33" s="1">
+        <v>158</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="D34" s="4">
+        <v>146</v>
+      </c>
+      <c r="E34" s="4">
+        <v>191</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G34" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H32" s="4" t="s">
+      <c r="H34" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="4" t="s">
+    <row r="35" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B35" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C35" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="D33" s="4">
+      <c r="D35" s="4">
         <v>241</v>
       </c>
-      <c r="E33" s="4">
+      <c r="E35" s="4">
         <v>286</v>
       </c>
-      <c r="F33" s="4" t="s">
+      <c r="F35" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="G33" s="4" t="s">
+      <c r="G35" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H33" s="4" t="s">
+      <c r="H35" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="34" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="5" t="s">
+    <row r="36" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B36" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C36" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="D34" s="5">
+      <c r="D36" s="5">
         <v>969</v>
       </c>
-      <c r="E34" s="5">
+      <c r="E36" s="5">
         <v>1102</v>
       </c>
-      <c r="F34" s="5" t="s">
+      <c r="F36" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G34" s="5" t="s">
+      <c r="G36" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H34" s="5" t="s">
+      <c r="H36" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="I34" s="5" t="s">
+      <c r="I36" s="5" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A35" s="1" t="s">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A37" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B37" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C37" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="D35" s="1">
+      <c r="D37" s="1">
         <v>335</v>
       </c>
-      <c r="E35" s="1">
+      <c r="E37" s="1">
         <v>467</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="F37" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G35" s="1" t="s">
+      <c r="G37" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="H35" s="1" t="s">
+      <c r="H37" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="36" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="4" t="s">
+    <row r="38" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B38" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C38" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="D36" s="4">
+      <c r="D38" s="4">
         <v>438</v>
       </c>
-      <c r="E36" s="4">
+      <c r="E38" s="4">
         <v>475</v>
       </c>
-      <c r="F36" s="4" t="s">
+      <c r="F38" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="G36" s="4" t="s">
+      <c r="G38" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H36" s="4" t="s">
+      <c r="H38" s="4" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="37" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="4" t="s">
+    <row r="39" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B39" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="C39" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="D37" s="4">
+      <c r="D39" s="4">
         <v>15</v>
       </c>
-      <c r="E37" s="4">
+      <c r="E39" s="4">
         <v>72</v>
       </c>
-      <c r="F37" s="4" t="s">
+      <c r="F39" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G37" s="4" t="s">
+      <c r="G39" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="H37" s="4" t="s">
+      <c r="H39" s="4" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="38" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="4" t="s">
+    <row r="40" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B40" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C40" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="D38" s="4">
+      <c r="D40" s="4">
         <v>17</v>
       </c>
-      <c r="E38" s="4">
+      <c r="E40" s="4">
         <v>74</v>
       </c>
-      <c r="F38" s="4" t="s">
+      <c r="F40" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G38" s="4" t="s">
+      <c r="G40" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="H38" s="4" t="s">
+      <c r="H40" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A39" s="1" t="s">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A41" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B41" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C41" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="D39" s="1">
+      <c r="D41" s="1">
         <v>489</v>
       </c>
-      <c r="E39" s="1">
+      <c r="E41" s="1">
         <v>612</v>
       </c>
-      <c r="F39" s="1" t="s">
+      <c r="F41" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G39" s="1" t="s">
+      <c r="G41" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H39" s="1" t="s">
+      <c r="H41" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A40" s="1" t="s">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A42" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B42" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C42" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="D40" s="1">
+      <c r="D42" s="1">
         <v>282</v>
       </c>
-      <c r="E40" s="1">
+      <c r="E42" s="1">
         <v>405</v>
       </c>
-      <c r="F40" s="1" t="s">
+      <c r="F42" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G40" s="1" t="s">
+      <c r="G42" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H40" s="1" t="s">
+      <c r="H42" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="41" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="4" t="s">
+    <row r="43" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B43" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="C43" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="D41" s="4">
+      <c r="D43" s="4">
         <v>65</v>
       </c>
-      <c r="E41" s="4">
+      <c r="E43" s="4">
         <v>85</v>
       </c>
-      <c r="F41" s="4" t="s">
+      <c r="F43" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G41" s="4" t="s">
+      <c r="G43" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H41" s="4" t="s">
+      <c r="H43" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="42" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="5" t="s">
+    <row r="44" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="B44" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="C44" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="D42" s="5">
+      <c r="D44" s="5">
         <v>13</v>
       </c>
-      <c r="E42" s="5">
+      <c r="E44" s="5">
         <v>128</v>
       </c>
-      <c r="F42" s="5" t="s">
+      <c r="F44" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G42" s="5" t="s">
+      <c r="G44" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="H42" s="5" t="s">
+      <c r="H44" s="5" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="43" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="4" t="s">
+    <row r="45" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="B45" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="C45" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="D43" s="4">
+      <c r="D45" s="4">
         <v>1</v>
       </c>
-      <c r="E43" s="4">
+      <c r="E45" s="4">
         <v>86</v>
       </c>
-      <c r="F43" s="4" t="s">
+      <c r="F45" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G43" s="4" t="s">
+      <c r="G45" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H43" s="4" t="s">
+      <c r="H45" s="4" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A44" s="1" t="s">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A46" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B46" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C46" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="D44" s="1">
+      <c r="D46" s="1">
         <v>295</v>
       </c>
-      <c r="E44" s="1">
+      <c r="E46" s="1">
         <v>301</v>
       </c>
-      <c r="F44" s="1" t="s">
+      <c r="F46" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G44" s="1" t="s">
+      <c r="G46" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H44" s="1" t="s">
+      <c r="H46" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="45" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="4" t="s">
+    <row r="47" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="B47" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C45" s="4" t="s">
+      <c r="C47" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="D45" s="4">
+      <c r="D47" s="4">
         <v>309</v>
       </c>
-      <c r="E45" s="4">
+      <c r="E47" s="4">
         <v>312</v>
       </c>
-      <c r="F45" s="4" t="s">
+      <c r="F47" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G45" s="4" t="s">
+      <c r="G47" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H45" s="4" t="s">
+      <c r="H47" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A46" s="1" t="s">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A48" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B48" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C48" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="D46" s="1">
+      <c r="D48" s="1">
         <v>296</v>
       </c>
-      <c r="E46" s="1">
+      <c r="E48" s="1">
         <v>298</v>
       </c>
-      <c r="F46" s="1" t="s">
+      <c r="F48" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="G46" s="1" t="s">
+      <c r="G48" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H46" s="1" t="s">
+      <c r="H48" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="47" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="4" t="s">
+    <row r="49" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="B49" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="C49" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="D47" s="4">
+      <c r="D49" s="4">
         <v>1173</v>
       </c>
-      <c r="E47" s="4">
+      <c r="E49" s="4">
         <v>1184</v>
       </c>
-      <c r="F47" s="4" t="s">
+      <c r="F49" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="G47" s="4" t="s">
+      <c r="G49" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H47" s="4" t="s">
+      <c r="H49" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A48" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="D48" s="1">
-        <v>564</v>
-      </c>
-      <c r="E48" s="1">
-        <v>594</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="H48" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A49" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="D49" s="1">
-        <v>611</v>
-      </c>
-      <c r="E49" s="1">
-        <v>641</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H49" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>92</v>
       </c>
@@ -2596,406 +2628,406 @@
         <v>220</v>
       </c>
       <c r="D50" s="1">
+        <v>564</v>
+      </c>
+      <c r="E50" s="1">
+        <v>594</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A51" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="D51" s="1">
+        <v>611</v>
+      </c>
+      <c r="E51" s="1">
+        <v>641</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A52" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="D52" s="1">
         <v>539</v>
       </c>
-      <c r="E50" s="1">
+      <c r="E52" s="1">
         <v>569</v>
       </c>
-      <c r="F50" s="1" t="s">
+      <c r="F52" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G50" s="1" t="s">
+      <c r="G52" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H50" s="1" t="s">
+      <c r="H52" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="51" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="4" t="s">
+    <row r="53" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B51" s="4" t="s">
+      <c r="B53" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="C51" s="4" t="s">
+      <c r="C53" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="D51" s="4">
+      <c r="D53" s="4">
         <v>88</v>
       </c>
-      <c r="F51" s="4" t="s">
+      <c r="F53" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G51" s="4" t="s">
+      <c r="G53" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="H51" s="4" t="s">
+      <c r="H53" s="4" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="52" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="4" t="s">
+    <row r="54" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="B54" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="C52" s="4" t="s">
+      <c r="C54" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="D52" s="4">
+      <c r="D54" s="4">
         <v>82</v>
       </c>
-      <c r="E52" s="4">
+      <c r="E54" s="4">
         <v>82</v>
       </c>
-      <c r="F52" s="4" t="s">
+      <c r="F54" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="G52" s="4" t="s">
+      <c r="G54" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="H52" s="4" t="s">
+      <c r="H54" s="4" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A53" s="1" t="s">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A55" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B55" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C55" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="D53" s="1">
+      <c r="D55" s="1">
         <v>1042</v>
       </c>
-      <c r="E53" s="1">
+      <c r="E55" s="1">
         <v>1056</v>
       </c>
-      <c r="F53" s="1" t="s">
+      <c r="F55" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G53" s="1" t="s">
+      <c r="G55" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H53" s="1" t="s">
+      <c r="H55" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A54" s="1" t="s">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A56" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="B56" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C56" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="D54" s="1">
+      <c r="D56" s="1">
         <v>2502</v>
       </c>
-      <c r="E54" s="1">
+      <c r="E56" s="1">
         <v>2608</v>
       </c>
-      <c r="F54" s="1" t="s">
+      <c r="F56" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G54" s="1" t="s">
+      <c r="G56" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H54" s="1" t="s">
+      <c r="H56" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="55" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="5" t="s">
+    <row r="57" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="B55" s="5" t="s">
+      <c r="B57" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C55" s="5" t="s">
+      <c r="C57" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="D55" s="5">
+      <c r="D57" s="5">
         <v>2038</v>
       </c>
-      <c r="E55" s="5">
+      <c r="E57" s="5">
         <v>2055</v>
       </c>
-      <c r="F55" s="5" t="s">
+      <c r="F57" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="G55" s="5" t="s">
+      <c r="G57" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="H55" s="5" t="s">
+      <c r="H57" s="5" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="56" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="5" t="s">
+    <row r="58" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="B56" s="5" t="s">
+      <c r="B58" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C56" s="5" t="s">
+      <c r="C58" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="D56" s="5">
+      <c r="D58" s="5">
         <v>2157</v>
       </c>
-      <c r="E56" s="5">
+      <c r="E58" s="5">
         <v>2174</v>
       </c>
-      <c r="F56" s="5" t="s">
+      <c r="F58" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="G56" s="5" t="s">
+      <c r="G58" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="H56" s="5" t="s">
+      <c r="H58" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="57" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="5" t="s">
+    <row r="59" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="B57" s="5" t="s">
+      <c r="B59" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C57" s="5" t="s">
+      <c r="C59" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="D57" s="5">
+      <c r="D59" s="5">
         <v>75</v>
       </c>
-      <c r="E57" s="5">
+      <c r="E59" s="5">
         <v>75</v>
       </c>
-      <c r="F57" s="5" t="s">
+      <c r="F59" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G57" s="5" t="s">
+      <c r="G59" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H57" s="5" t="s">
+      <c r="H59" s="5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="58" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="4" t="s">
+    <row r="60" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B58" s="4" t="s">
+      <c r="B60" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="C58" s="4" t="s">
+      <c r="C60" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="D58" s="4">
+      <c r="D60" s="4">
         <v>936</v>
       </c>
-      <c r="E58" s="4">
+      <c r="E60" s="4">
         <v>1122</v>
       </c>
-      <c r="F58" s="4" t="s">
+      <c r="F60" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="G58" s="4" t="s">
+      <c r="G60" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H58" s="4" t="s">
+      <c r="H60" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="59" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="4" t="s">
+    <row r="61" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B59" s="4" t="s">
+      <c r="B61" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="C59" s="4" t="s">
+      <c r="C61" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="D59" s="4">
+      <c r="D61" s="4">
         <v>358</v>
       </c>
-      <c r="E59" s="4">
+      <c r="E61" s="4">
         <v>526</v>
       </c>
-      <c r="F59" s="4" t="s">
+      <c r="F61" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G59" s="4" t="s">
+      <c r="G61" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H59" s="4" t="s">
+      <c r="H61" s="4" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="60" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="4" t="s">
+    <row r="62" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="B60" s="4" t="s">
+      <c r="B62" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="C60" s="4" t="s">
+      <c r="C62" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="D60" s="4">
+      <c r="D62" s="4">
         <v>3</v>
       </c>
-      <c r="E60" s="4">
+      <c r="E62" s="4">
         <v>19</v>
       </c>
-      <c r="F60" s="4" t="s">
+      <c r="F62" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G60" s="4" t="s">
+      <c r="G62" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="H60" s="4" t="s">
+      <c r="H62" s="4" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="61" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="4" t="s">
+    <row r="63" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="B61" s="4" t="s">
+      <c r="B63" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="C61" s="4" t="s">
+      <c r="C63" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="D61" s="4">
+      <c r="D63" s="4">
         <v>1</v>
       </c>
-      <c r="E61" s="4">
+      <c r="E63" s="4">
         <v>71</v>
       </c>
-      <c r="F61" s="4" t="s">
+      <c r="F63" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G61" s="4" t="s">
+      <c r="G63" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="H61" s="4" t="s">
+      <c r="H63" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A62" s="1" t="s">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A64" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B64" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="C64" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="D62" s="1">
+      <c r="D64" s="1">
         <v>318</v>
       </c>
-      <c r="F62" s="1" t="s">
+      <c r="F64" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G62" s="1" t="s">
+      <c r="G64" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H62" s="1" t="s">
+      <c r="H64" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A63" s="1" t="s">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A65" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B65" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C65" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="D63" s="1">
+      <c r="D65" s="1">
         <v>388</v>
       </c>
-      <c r="E63" s="1">
+      <c r="E65" s="1">
         <v>540</v>
       </c>
-      <c r="F63" s="1" t="s">
+      <c r="F65" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G63" s="1" t="s">
+      <c r="G65" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="H63" s="1" t="s">
+      <c r="H65" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="64" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="B64" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="C64" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="D64" s="4">
-        <v>94</v>
-      </c>
-      <c r="E64" s="4">
-        <v>211</v>
-      </c>
-      <c r="F64" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="G64" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H64" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="B65" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="C65" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="D65" s="4">
-        <v>496</v>
-      </c>
-      <c r="E65" s="4">
-        <v>648</v>
-      </c>
-      <c r="F65" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="G65" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H65" s="4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A66" s="4" t="s">
         <v>121</v>
       </c>
@@ -3006,161 +3038,161 @@
         <v>230</v>
       </c>
       <c r="D66" s="4">
+        <v>94</v>
+      </c>
+      <c r="E66" s="4">
+        <v>211</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G66" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H66" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="D67" s="4">
+        <v>496</v>
+      </c>
+      <c r="E67" s="4">
+        <v>648</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G67" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H67" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="D68" s="4">
         <v>113</v>
       </c>
-      <c r="E66" s="4">
+      <c r="E68" s="4">
         <v>230</v>
       </c>
-      <c r="F66" s="4" t="s">
+      <c r="F68" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="G66" s="4" t="s">
+      <c r="G68" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="H66" s="4" t="s">
+      <c r="H68" s="4" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="67" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="9" t="s">
+    <row r="69" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="B67" s="9" t="s">
+      <c r="B69" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="C67" s="9" t="s">
+      <c r="C69" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="D67" s="9">
+      <c r="D69" s="9">
         <v>223</v>
       </c>
-      <c r="E67" s="9">
+      <c r="E69" s="9">
         <v>249</v>
       </c>
-      <c r="F67" s="9" t="s">
+      <c r="F69" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="G67" s="9" t="s">
+      <c r="G69" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="H67" s="9" t="s">
+      <c r="H69" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="I67" s="9" t="s">
+      <c r="I69" s="9" t="s">
         <v>263</v>
       </c>
-      <c r="J67" s="9" t="s">
+      <c r="J69" s="9" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="68" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="7" t="s">
+    <row r="70" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="B68" s="7" t="s">
+      <c r="B70" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="C68" s="7" t="s">
+      <c r="C70" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="D68" s="7">
+      <c r="D70" s="7">
         <v>502</v>
       </c>
-      <c r="E68" s="7">
+      <c r="E70" s="7">
         <v>506</v>
       </c>
-      <c r="F68" s="7" t="s">
+      <c r="F70" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="G68" s="7" t="s">
+      <c r="G70" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="H68" s="7" t="s">
+      <c r="H70" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="J68" s="7" t="s">
+      <c r="J70" s="7" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="69" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="6" t="s">
+    <row r="71" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="B69" s="6" t="s">
+      <c r="B71" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="C69" s="6" t="s">
+      <c r="C71" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="D69" s="6">
+      <c r="D71" s="6">
         <v>535</v>
       </c>
-      <c r="E69" s="6">
+      <c r="E71" s="6">
         <v>539</v>
       </c>
-      <c r="F69" s="6" t="s">
+      <c r="F71" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G69" s="6" t="s">
+      <c r="G71" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H69" s="6" t="s">
+      <c r="H71" s="6" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="70" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="C70" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="D70" s="5">
-        <v>227</v>
-      </c>
-      <c r="E70" s="5">
-        <v>229</v>
-      </c>
-      <c r="F70" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="G70" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H70" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="C71" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="D71" s="5">
-        <v>351</v>
-      </c>
-      <c r="E71" s="5">
-        <v>353</v>
-      </c>
-      <c r="F71" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="G71" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="H71" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A72" s="5" t="s">
         <v>128</v>
       </c>
@@ -3171,22 +3203,22 @@
         <v>232</v>
       </c>
       <c r="D72" s="5">
-        <v>350</v>
+        <v>227</v>
       </c>
       <c r="E72" s="5">
-        <v>352</v>
+        <v>229</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>11</v>
+        <v>94</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A73" s="5" t="s">
         <v>128</v>
       </c>
@@ -3197,308 +3229,308 @@
         <v>232</v>
       </c>
       <c r="D73" s="5">
+        <v>351</v>
+      </c>
+      <c r="E73" s="5">
+        <v>353</v>
+      </c>
+      <c r="F73" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="G73" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H73" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="D74" s="5">
+        <v>350</v>
+      </c>
+      <c r="E74" s="5">
+        <v>352</v>
+      </c>
+      <c r="F74" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G74" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H74" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="D75" s="5">
         <v>416</v>
       </c>
-      <c r="E73" s="5">
+      <c r="E75" s="5">
         <v>419</v>
       </c>
-      <c r="F73" s="5" t="s">
+      <c r="F75" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G73" s="5" t="s">
+      <c r="G75" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="H73" s="5" t="s">
+      <c r="H75" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A74" s="1" t="s">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A76" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="B76" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="C76" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="D74" s="1">
+      <c r="D76" s="1">
         <v>426</v>
       </c>
-      <c r="E74" s="1">
+      <c r="E76" s="1">
         <v>429</v>
       </c>
-      <c r="F74" s="1" t="s">
+      <c r="F76" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G74" s="1" t="s">
+      <c r="G76" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H74" s="1" t="s">
+      <c r="H76" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A75" s="1" t="s">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A77" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="B77" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="C77" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="D75" s="1">
+      <c r="D77" s="1">
         <v>230</v>
       </c>
-      <c r="E75" s="1">
+      <c r="E77" s="1">
         <v>232</v>
       </c>
-      <c r="F75" s="1" t="s">
+      <c r="F77" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G75" s="1" t="s">
+      <c r="G77" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H75" s="1" t="s">
+      <c r="H77" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="76" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="5" t="s">
+    <row r="78" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="B76" s="5" t="s">
+      <c r="B78" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="C76" s="5" t="s">
+      <c r="C78" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="D76" s="5">
+      <c r="D78" s="5">
         <v>351</v>
       </c>
-      <c r="E76" s="5">
+      <c r="E78" s="5">
         <v>353</v>
       </c>
-      <c r="F76" s="5" t="s">
+      <c r="F78" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="G76" s="5" t="s">
+      <c r="G78" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="H76" s="5" t="s">
+      <c r="H78" s="5" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="77" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="4" t="s">
+    <row r="79" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="B77" s="4" t="s">
+      <c r="B79" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="C77" s="4" t="s">
+      <c r="C79" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="D77" s="4">
+      <c r="D79" s="4">
         <v>391</v>
       </c>
-      <c r="E77" s="4">
+      <c r="E79" s="4">
         <v>394</v>
       </c>
-      <c r="F77" s="4" t="s">
+      <c r="F79" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="G77" s="4" t="s">
+      <c r="G79" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="H77" s="4" t="s">
+      <c r="H79" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A78" s="1" t="s">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A80" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="B80" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="C80" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="D78" s="1">
+      <c r="D80" s="1">
         <v>298</v>
       </c>
-      <c r="E78" s="1">
+      <c r="E80" s="1">
         <v>347</v>
       </c>
-      <c r="F78" s="1" t="s">
+      <c r="F80" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G78" s="1" t="s">
+      <c r="G80" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="H78" s="1" t="s">
+      <c r="H80" s="1" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="79" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="4" t="s">
+    <row r="81" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="B79" s="4" t="s">
+      <c r="B81" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="C79" s="4" t="s">
+      <c r="C81" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="D79" s="4">
+      <c r="D81" s="4">
         <v>191</v>
       </c>
-      <c r="E79" s="4">
+      <c r="E81" s="4">
         <v>240</v>
       </c>
-      <c r="F79" s="4" t="s">
+      <c r="F81" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G79" s="4" t="s">
+      <c r="G81" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H79" s="4" t="s">
+      <c r="H81" s="4" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A80" s="1" t="s">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A82" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B80" s="1" t="s">
+      <c r="B82" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="C82" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="D80" s="1">
+      <c r="D82" s="1">
         <v>102</v>
       </c>
-      <c r="E80" s="1">
+      <c r="E82" s="1">
         <v>102</v>
       </c>
-      <c r="F80" s="1" t="s">
+      <c r="F82" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G80" s="1" t="s">
+      <c r="G82" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H80" s="1" t="s">
+      <c r="H82" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A81" s="1" t="s">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A83" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="B83" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="C83" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="D81" s="1">
+      <c r="D83" s="1">
         <v>53</v>
       </c>
-      <c r="E81" s="1">
+      <c r="E83" s="1">
         <v>53</v>
       </c>
-      <c r="F81" s="1" t="s">
+      <c r="F83" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G81" s="1" t="s">
+      <c r="G83" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H81" s="1" t="s">
+      <c r="H83" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A82" s="1" t="s">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A84" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="B84" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="C84" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="D82" s="1">
+      <c r="D84" s="1">
         <v>114</v>
       </c>
-      <c r="E82" s="1">
+      <c r="E84" s="1">
         <v>307</v>
       </c>
-      <c r="F82" s="1" t="s">
+      <c r="F84" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G82" s="1" t="s">
+      <c r="G84" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H82" s="1" t="s">
+      <c r="H84" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="83" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="B83" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="C83" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="D83" s="4">
-        <v>115</v>
-      </c>
-      <c r="E83" s="4">
-        <v>308</v>
-      </c>
-      <c r="F83" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="G83" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H83" s="4" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="B84" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="C84" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="D84" s="4">
-        <v>125</v>
-      </c>
-      <c r="E84" s="4">
-        <v>318</v>
-      </c>
-      <c r="F84" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="G84" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="H84" s="4" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A85" s="4" t="s">
         <v>137</v>
       </c>
@@ -3509,22 +3541,22 @@
         <v>236</v>
       </c>
       <c r="D85" s="4">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E85" s="4">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="H85" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A86" s="4" t="s">
         <v>137</v>
       </c>
@@ -3535,77 +3567,74 @@
         <v>236</v>
       </c>
       <c r="D86" s="4">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="E86" s="4">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A87" s="4" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D87" s="4">
-        <v>46</v>
+        <v>117</v>
       </c>
       <c r="E87" s="4">
-        <v>83</v>
+        <v>310</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G87" s="4" t="s">
         <v>21</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J87" s="10" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A88" s="4" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D88" s="4">
-        <v>583</v>
+        <v>119</v>
       </c>
       <c r="E88" s="4">
-        <v>631</v>
+        <v>312</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="H88" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A89" s="4" t="s">
         <v>144</v>
       </c>
@@ -3616,51 +3645,51 @@
         <v>237</v>
       </c>
       <c r="D89" s="4">
-        <v>579</v>
+        <v>46</v>
       </c>
       <c r="E89" s="4">
-        <v>627</v>
+        <v>83</v>
       </c>
       <c r="F89" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G89" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H89" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J89" s="10" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="D90" s="4">
+        <v>583</v>
+      </c>
+      <c r="E90" s="4">
+        <v>631</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G90" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G89" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H89" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="B90" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="C90" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="D90" s="6">
-        <v>88</v>
-      </c>
-      <c r="E90" s="6">
-        <v>125</v>
-      </c>
-      <c r="F90" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="G90" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="I90" s="6" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H90" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A91" s="4" t="s">
         <v>144</v>
       </c>
@@ -3671,74 +3700,77 @@
         <v>237</v>
       </c>
       <c r="D91" s="4">
-        <v>301</v>
+        <v>579</v>
       </c>
       <c r="E91" s="4">
-        <v>343</v>
+        <v>627</v>
       </c>
       <c r="F91" s="4" t="s">
         <v>41</v>
       </c>
       <c r="G91" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H91" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="D92" s="6">
+        <v>88</v>
+      </c>
+      <c r="E92" s="6">
+        <v>125</v>
+      </c>
+      <c r="F92" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G92" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H92" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I92" s="6" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="D93" s="4">
+        <v>301</v>
+      </c>
+      <c r="E93" s="4">
+        <v>343</v>
+      </c>
+      <c r="F93" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G93" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="H91" s="4" t="s">
+      <c r="H93" s="4" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="92" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="B92" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="C92" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="D92" s="4">
-        <v>35</v>
-      </c>
-      <c r="E92" s="4">
-        <v>44</v>
-      </c>
-      <c r="F92" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G92" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H92" s="4" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A93" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="D93" s="1">
-        <v>309</v>
-      </c>
-      <c r="E93" s="1">
-        <v>446</v>
-      </c>
-      <c r="F93" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G93" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H93" s="1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A94" s="4" t="s">
         <v>147</v>
       </c>
@@ -3749,568 +3781,568 @@
         <v>238</v>
       </c>
       <c r="D94" s="4">
+        <v>35</v>
+      </c>
+      <c r="E94" s="4">
+        <v>44</v>
+      </c>
+      <c r="F94" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G94" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H94" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A95" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="D95" s="1">
+        <v>309</v>
+      </c>
+      <c r="E95" s="1">
+        <v>446</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H95" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="D96" s="4">
         <v>1</v>
       </c>
-      <c r="E94" s="4">
+      <c r="E96" s="4">
         <v>10</v>
       </c>
-      <c r="F94" s="4" t="s">
+      <c r="F96" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G94" s="4" t="s">
+      <c r="G96" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H94" s="4" t="s">
+      <c r="H96" s="4" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A95" s="1" t="s">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A97" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B95" s="1" t="s">
+      <c r="B97" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="C95" s="1" t="s">
+      <c r="C97" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="D95" s="1">
+      <c r="D97" s="1">
         <v>372</v>
       </c>
-      <c r="E95" s="1">
+      <c r="E97" s="1">
         <v>519</v>
       </c>
-      <c r="F95" s="1" t="s">
+      <c r="F97" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G95" s="1" t="s">
+      <c r="G97" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="H95" s="1" t="s">
+      <c r="H97" s="1" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A96" s="1" t="s">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A98" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B96" s="1" t="s">
+      <c r="B98" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="C96" s="1" t="s">
+      <c r="C98" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="D96" s="1">
+      <c r="D98" s="1">
         <v>167</v>
       </c>
-      <c r="E96" s="1">
+      <c r="E98" s="1">
         <v>297</v>
       </c>
-      <c r="F96" s="1" t="s">
+      <c r="F98" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G96" s="1" t="s">
+      <c r="G98" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H96" s="1" t="s">
+      <c r="H98" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A97" s="1" t="s">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A99" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B97" s="1" t="s">
+      <c r="B99" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C97" s="1" t="s">
+      <c r="C99" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="D97" s="1">
+      <c r="D99" s="1">
         <v>780</v>
       </c>
-      <c r="E97" s="1">
+      <c r="E99" s="1">
         <v>822</v>
       </c>
-      <c r="F97" s="1" t="s">
+      <c r="F99" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G97" s="1" t="s">
+      <c r="G99" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H97" s="1" t="s">
+      <c r="H99" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A98" s="1" t="s">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A100" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="B100" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C98" s="1" t="s">
+      <c r="C100" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="D98" s="1">
+      <c r="D100" s="1">
         <v>164</v>
       </c>
-      <c r="E98" s="1">
+      <c r="E100" s="1">
         <v>185</v>
       </c>
-      <c r="F98" s="1" t="s">
+      <c r="F100" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="G98" s="1" t="s">
+      <c r="G100" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="H98" s="1" t="s">
+      <c r="H100" s="1" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="99" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="5" t="s">
+    <row r="101" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A101" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="B99" s="5" t="s">
+      <c r="B101" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="C99" s="5" t="s">
+      <c r="C101" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="D99" s="5">
+      <c r="D101" s="5">
         <v>176</v>
       </c>
-      <c r="E99" s="5">
+      <c r="E101" s="5">
         <v>197</v>
       </c>
-      <c r="F99" s="5" t="s">
+      <c r="F101" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G99" s="5" t="s">
+      <c r="G101" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H99" s="5" t="s">
+      <c r="H101" s="5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="100" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="5" t="s">
+    <row r="102" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A102" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="B100" s="5" t="s">
+      <c r="B102" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="C100" s="5" t="s">
+      <c r="C102" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="D100" s="5">
+      <c r="D102" s="5">
         <v>413</v>
       </c>
-      <c r="E100" s="5">
+      <c r="E102" s="5">
         <v>434</v>
       </c>
-      <c r="F100" s="5" t="s">
+      <c r="F102" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G100" s="5" t="s">
+      <c r="G102" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="H100" s="5" t="s">
+      <c r="H102" s="5" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A101" s="1" t="s">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A103" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="B103" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C101" s="1" t="s">
+      <c r="C103" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="D101" s="1">
+      <c r="D103" s="1">
         <v>156</v>
       </c>
-      <c r="E101" s="1">
+      <c r="E103" s="1">
         <v>177</v>
       </c>
-      <c r="F101" s="1" t="s">
+      <c r="F103" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G101" s="1" t="s">
+      <c r="G103" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H101" s="1" t="s">
+      <c r="H103" s="1" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="102" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="4" t="s">
+    <row r="104" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A104" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="B102" s="4" t="s">
+      <c r="B104" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="C102" s="4" t="s">
+      <c r="C104" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="D102" s="4">
+      <c r="D104" s="4">
         <v>271</v>
       </c>
-      <c r="E102" s="4">
+      <c r="E104" s="4">
         <v>278</v>
       </c>
-      <c r="F102" s="4" t="s">
+      <c r="F104" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G102" s="4" t="s">
+      <c r="G104" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H102" s="4" t="s">
+      <c r="H104" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A103" s="1" t="s">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A105" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B103" s="1" t="s">
+      <c r="B105" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="C103" s="1" t="s">
+      <c r="C105" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="D103" s="1">
+      <c r="D105" s="1">
         <v>1</v>
       </c>
-      <c r="E103" s="1">
+      <c r="E105" s="1">
         <v>83</v>
       </c>
-      <c r="F103" s="1" t="s">
+      <c r="F105" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G103" s="1" t="s">
+      <c r="G105" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H103" s="1" t="s">
+      <c r="H105" s="1" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A104" s="1" t="s">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A106" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B104" s="1" t="s">
+      <c r="B106" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="C104" s="1" t="s">
+      <c r="C106" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="D104" s="1">
+      <c r="D106" s="1">
         <v>760</v>
       </c>
-      <c r="E104" s="1">
+      <c r="E106" s="1">
         <v>765</v>
       </c>
-      <c r="F104" s="1" t="s">
+      <c r="F106" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G104" s="1" t="s">
+      <c r="G106" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H104" s="1" t="s">
+      <c r="H106" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="105" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="4" t="s">
+    <row r="107" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A107" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="B105" s="4" t="s">
+      <c r="B107" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="C105" s="4" t="s">
+      <c r="C107" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="D105" s="4">
+      <c r="D107" s="4">
         <v>237</v>
       </c>
-      <c r="E105" s="4">
+      <c r="E107" s="4">
         <v>271</v>
       </c>
-      <c r="F105" s="4" t="s">
+      <c r="F107" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="G105" s="4" t="s">
+      <c r="G107" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H105" s="4" t="s">
+      <c r="H107" s="4" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="106" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="4" t="s">
+    <row r="108" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A108" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="B106" s="4" t="s">
+      <c r="B108" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="C106" s="4" t="s">
+      <c r="C108" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="D106" s="4">
+      <c r="D108" s="4">
         <v>239</v>
       </c>
-      <c r="E106" s="4">
+      <c r="E108" s="4">
         <v>273</v>
       </c>
-      <c r="F106" s="4" t="s">
+      <c r="F108" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G106" s="4" t="s">
+      <c r="G108" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H106" s="4" t="s">
+      <c r="H108" s="4" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A107" s="1" t="s">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A109" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B107" s="1" t="s">
+      <c r="B109" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="C107" s="1" t="s">
+      <c r="C109" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="D107" s="1">
+      <c r="D109" s="1">
         <v>1021</v>
       </c>
-      <c r="E107" s="1">
+      <c r="E109" s="1">
         <v>1342</v>
       </c>
-      <c r="F107" s="1" t="s">
+      <c r="F109" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G107" s="1" t="s">
+      <c r="G109" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="H107" s="1" t="s">
+      <c r="H109" s="1" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A108" s="1" t="s">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A110" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="B108" s="1" t="s">
+      <c r="B110" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="C108" s="1" t="s">
+      <c r="C110" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="D108" s="1">
+      <c r="D110" s="1">
         <v>793</v>
       </c>
-      <c r="E108" s="1">
+      <c r="E110" s="1">
         <v>808</v>
       </c>
-      <c r="F108" s="1" t="s">
+      <c r="F110" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G108" s="1" t="s">
+      <c r="G110" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H108" s="1" t="s">
+      <c r="H110" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="109" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="4" t="s">
+    <row r="111" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A111" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="B109" s="4" t="s">
+      <c r="B111" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="C109" s="4" t="s">
+      <c r="C111" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="D109" s="4">
+      <c r="D111" s="4">
         <v>1</v>
       </c>
-      <c r="E109" s="4">
+      <c r="E111" s="4">
         <v>54</v>
       </c>
-      <c r="F109" s="4" t="s">
+      <c r="F111" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G109" s="4" t="s">
+      <c r="G111" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="H109" s="4" t="s">
+      <c r="H111" s="4" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A110" s="1" t="s">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A112" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B110" s="1" t="s">
+      <c r="B112" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="C110" s="1" t="s">
+      <c r="C112" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="D110" s="1">
+      <c r="D112" s="1">
         <v>422</v>
       </c>
-      <c r="E110" s="1">
+      <c r="E112" s="1">
         <v>429</v>
       </c>
-      <c r="F110" s="1" t="s">
+      <c r="F112" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G110" s="1" t="s">
+      <c r="G112" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="H110" s="1" t="s">
+      <c r="H112" s="1" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A111" s="1" t="s">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A113" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B111" s="1" t="s">
+      <c r="B113" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="C111" s="1" t="s">
+      <c r="C113" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="D111" s="1">
+      <c r="D113" s="1">
         <v>815</v>
       </c>
-      <c r="E111" s="1">
+      <c r="E113" s="1">
         <v>830</v>
       </c>
-      <c r="F111" s="1" t="s">
+      <c r="F113" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="G111" s="1" t="s">
+      <c r="G113" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="H111" s="1" t="s">
+      <c r="H113" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A112" s="1" t="s">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A114" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B112" s="1" t="s">
+      <c r="B114" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="C112" s="1" t="s">
+      <c r="C114" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="D112" s="1">
+      <c r="D114" s="1">
         <v>92</v>
       </c>
-      <c r="E112" s="1">
+      <c r="E114" s="1">
         <v>92</v>
       </c>
-      <c r="F112" s="1" t="s">
+      <c r="F114" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G112" s="1" t="s">
+      <c r="G114" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H112" s="1" t="s">
+      <c r="H114" s="1" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="113" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="6" t="s">
+    <row r="115" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A115" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="B113" s="6" t="s">
+      <c r="B115" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="C113" s="6" t="s">
+      <c r="C115" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="D113" s="6">
+      <c r="D115" s="6">
         <v>142</v>
       </c>
-      <c r="E113" s="6">
+      <c r="E115" s="6">
         <v>142</v>
       </c>
-      <c r="F113" s="6" t="s">
+      <c r="F115" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="G113" s="6" t="s">
+      <c r="G115" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="H113" s="6" t="s">
+      <c r="H115" s="6" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="114" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="B114" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="C114" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="D114" s="5">
-        <v>127</v>
-      </c>
-      <c r="E114" s="5">
-        <v>127</v>
-      </c>
-      <c r="F114" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="G114" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H114" s="5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="115" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="B115" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="C115" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="D115" s="5">
-        <v>82</v>
-      </c>
-      <c r="E115" s="5">
-        <v>82</v>
-      </c>
-      <c r="F115" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="G115" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H115" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="116" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A116" s="5" t="s">
         <v>187</v>
       </c>
@@ -4321,22 +4353,22 @@
         <v>252</v>
       </c>
       <c r="D116" s="5">
-        <v>77</v>
+        <v>127</v>
       </c>
       <c r="E116" s="5">
-        <v>77</v>
+        <v>127</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="G116" s="5" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="H116" s="5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="117" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A117" s="5" t="s">
         <v>187</v>
       </c>
@@ -4347,100 +4379,100 @@
         <v>252</v>
       </c>
       <c r="D117" s="5">
+        <v>82</v>
+      </c>
+      <c r="E117" s="5">
+        <v>82</v>
+      </c>
+      <c r="F117" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="G117" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H117" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A118" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B118" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="C118" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="D118" s="5">
+        <v>77</v>
+      </c>
+      <c r="E118" s="5">
+        <v>77</v>
+      </c>
+      <c r="F118" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G118" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H118" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A119" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B119" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="C119" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="D119" s="5">
         <v>126</v>
       </c>
-      <c r="E117" s="5">
+      <c r="E119" s="5">
         <v>126</v>
       </c>
-      <c r="F117" s="5" t="s">
+      <c r="F119" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="G117" s="5" t="s">
+      <c r="G119" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="H117" s="5" t="s">
+      <c r="H119" s="5" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A118" s="1" t="s">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A120" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="B118" s="1" t="s">
+      <c r="B120" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="C118" s="1" t="s">
+      <c r="C120" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="D118" s="1">
+      <c r="D120" s="1">
         <v>3719</v>
       </c>
-      <c r="E118" s="1">
+      <c r="E120" s="1">
         <v>3733</v>
       </c>
-      <c r="F118" s="1" t="s">
+      <c r="F120" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G118" s="1" t="s">
+      <c r="G120" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H118" s="1" t="s">
+      <c r="H120" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="119" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="B119" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="C119" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="D119" s="4">
-        <v>151</v>
-      </c>
-      <c r="E119" s="4">
-        <v>216</v>
-      </c>
-      <c r="F119" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="G119" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H119" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="120" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="B120" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="C120" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="D120" s="4">
-        <v>132</v>
-      </c>
-      <c r="E120" s="4">
-        <v>195</v>
-      </c>
-      <c r="F120" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G120" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H120" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="121" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A121" s="4" t="s">
         <v>191</v>
       </c>
@@ -4451,22 +4483,22 @@
         <v>254</v>
       </c>
       <c r="D121" s="4">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E121" s="4">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="H121" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="122" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A122" s="4" t="s">
         <v>191</v>
       </c>
@@ -4477,22 +4509,22 @@
         <v>254</v>
       </c>
       <c r="D122" s="4">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="E122" s="4">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H122" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="123" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A123" s="4" t="s">
         <v>191</v>
       </c>
@@ -4503,22 +4535,22 @@
         <v>254</v>
       </c>
       <c r="D123" s="4">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="E123" s="4">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H123" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="124" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A124" s="4" t="s">
         <v>191</v>
       </c>
@@ -4529,99 +4561,151 @@
         <v>254</v>
       </c>
       <c r="D124" s="4">
+        <v>114</v>
+      </c>
+      <c r="E124" s="4">
+        <v>177</v>
+      </c>
+      <c r="F124" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G124" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H124" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A125" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B125" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="C125" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="D125" s="4">
+        <v>161</v>
+      </c>
+      <c r="E125" s="4">
+        <v>226</v>
+      </c>
+      <c r="F125" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G125" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H125" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A126" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B126" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="C126" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="D126" s="4">
         <v>170</v>
       </c>
-      <c r="E124" s="4">
+      <c r="E126" s="4">
         <v>244</v>
       </c>
-      <c r="F124" s="4" t="s">
+      <c r="F126" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="G124" s="4" t="s">
+      <c r="G126" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H124" s="4" t="s">
+      <c r="H126" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="125" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="4" t="s">
+    <row r="127" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A127" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="B125" s="4" t="s">
+      <c r="B127" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="C125" s="4" t="s">
+      <c r="C127" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="D125" s="4">
+      <c r="D127" s="4">
         <v>528</v>
       </c>
-      <c r="E125" s="4">
+      <c r="E127" s="4">
         <v>563</v>
       </c>
-      <c r="F125" s="4" t="s">
+      <c r="F127" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="G125" s="4" t="s">
+      <c r="G127" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H125" s="4" t="s">
+      <c r="H127" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="126" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="8" t="s">
+    <row r="128" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A128" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="B126" s="8" t="s">
+      <c r="B128" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="C126" s="8" t="s">
+      <c r="C128" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="D126" s="8">
+      <c r="D128" s="8">
         <v>341</v>
       </c>
-      <c r="E126" s="8">
+      <c r="E128" s="8">
         <v>523</v>
       </c>
-      <c r="F126" s="8" t="s">
+      <c r="F128" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G126" s="8" t="s">
+      <c r="G128" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="H126" s="8" t="s">
+      <c r="H128" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="J126" s="8" t="s">
+      <c r="J128" s="8" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A127" s="1" t="s">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A129" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B127" s="1" t="s">
+      <c r="B129" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="C127" s="1" t="s">
+      <c r="C129" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="D127" s="1">
+      <c r="D129" s="1">
         <v>1049</v>
       </c>
-      <c r="E127" s="1">
+      <c r="E129" s="1">
         <v>1091</v>
       </c>
-      <c r="F127" s="1" t="s">
+      <c r="F129" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G127" s="1" t="s">
+      <c r="G129" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H127" s="1" t="s">
+      <c r="H129" s="1" t="s">
         <v>56</v>
       </c>
     </row>

--- a/Outputs_primates/AllGenes_Potential_CPDs.xlsx
+++ b/Outputs_primates/AllGenes_Potential_CPDs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adesinamary/Downloads/kondrashov/Outputs_primates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7115085-B8C9-E948-9630-677186C5056D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DE7A887-EF3E-EB4A-B22C-4948E71FD544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="23260" windowHeight="12460" xr2:uid="{BC6F7999-E049-F441-AF63-5F5D062E3B8F}"/>
   </bookViews>
@@ -53,12 +53,6 @@
     <t>wild</t>
   </si>
   <si>
-    <t>mut</t>
-  </si>
-  <si>
-    <t>var</t>
-  </si>
-  <si>
     <t>ACADM</t>
   </si>
   <si>
@@ -867,6 +861,12 @@
   </si>
   <si>
     <t xml:space="preserve"> ['S']</t>
+  </si>
+  <si>
+    <t>muts</t>
+  </si>
+  <si>
+    <t>variable_amino_acids</t>
   </si>
 </sst>
 </file>
@@ -1341,39 +1341,39 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>4</v>
+        <v>274</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>5</v>
+        <v>275</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D2" s="1">
         <v>29</v>
@@ -1382,25 +1382,25 @@
         <v>117</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="J2" s="3"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D3" s="1">
         <v>31</v>
@@ -1409,24 +1409,24 @@
         <v>1119</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D4" s="1">
         <v>103</v>
@@ -1435,24 +1435,24 @@
         <v>191</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D5" s="1">
         <v>29</v>
@@ -1461,24 +1461,24 @@
         <v>117</v>
       </c>
       <c r="F5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D6" s="12">
         <v>174</v>
@@ -1487,24 +1487,24 @@
         <v>221</v>
       </c>
       <c r="F6" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="H6" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>271</v>
-      </c>
-      <c r="H6" s="12" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D7" s="12">
         <v>219</v>
@@ -1513,24 +1513,24 @@
         <v>266</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D8" s="5">
         <v>286</v>
@@ -1539,24 +1539,24 @@
         <v>333</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D9" s="4">
         <v>1</v>
@@ -1565,24 +1565,24 @@
         <v>115</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D10" s="4">
         <v>1</v>
@@ -1591,24 +1591,24 @@
         <v>115</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D11" s="4">
         <v>15</v>
@@ -1617,24 +1617,24 @@
         <v>54</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D12" s="4">
         <v>17</v>
@@ -1643,24 +1643,24 @@
         <v>56</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D13" s="1">
         <v>156</v>
@@ -1669,24 +1669,24 @@
         <v>260</v>
       </c>
       <c r="F13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H13" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D14" s="4">
         <v>260</v>
@@ -1695,24 +1695,24 @@
         <v>364</v>
       </c>
       <c r="F14" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H14" s="4" t="s">
         <v>36</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D15" s="1">
         <v>82</v>
@@ -1721,24 +1721,24 @@
         <v>105</v>
       </c>
       <c r="F15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H15" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D16" s="4">
         <v>383</v>
@@ -1747,24 +1747,24 @@
         <v>397</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D17" s="4">
         <v>21</v>
@@ -1773,24 +1773,24 @@
         <v>184</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D18" s="4">
         <v>1</v>
@@ -1799,24 +1799,24 @@
         <v>164</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D19" s="1">
         <v>2378</v>
@@ -1825,24 +1825,24 @@
         <v>3867</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D20" s="4">
         <v>1155</v>
@@ -1851,24 +1851,24 @@
         <v>2307</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D21" s="1">
         <v>1459</v>
@@ -1877,24 +1877,24 @@
         <v>2851</v>
       </c>
       <c r="F21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H21" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D22" s="1">
         <v>2465</v>
@@ -1903,24 +1903,24 @@
         <v>3954</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D23" s="4">
         <v>51</v>
@@ -1929,24 +1929,24 @@
         <v>94</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D24" s="4">
         <v>82</v>
@@ -1955,24 +1955,24 @@
         <v>128</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D25" s="1">
         <v>82</v>
@@ -1981,24 +1981,24 @@
         <v>128</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D26" s="4">
         <v>85</v>
@@ -2007,24 +2007,24 @@
         <v>138</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D27" s="1">
         <v>93</v>
@@ -2033,24 +2033,24 @@
         <v>155</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D28" s="1">
         <v>295</v>
@@ -2059,24 +2059,24 @@
         <v>372</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D29" s="4">
         <v>97</v>
@@ -2085,24 +2085,24 @@
         <v>150</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D30" s="4">
         <v>85</v>
@@ -2111,24 +2111,24 @@
         <v>138</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D31" s="1">
         <v>152</v>
@@ -2137,24 +2137,24 @@
         <v>205</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="32" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D32" s="4">
         <v>95</v>
@@ -2163,24 +2163,24 @@
         <v>148</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D33" s="1">
         <v>113</v>
@@ -2189,24 +2189,24 @@
         <v>158</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="34" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D34" s="4">
         <v>146</v>
@@ -2215,24 +2215,24 @@
         <v>191</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D35" s="4">
         <v>241</v>
@@ -2241,24 +2241,24 @@
         <v>286</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="36" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D36" s="5">
         <v>969</v>
@@ -2267,27 +2267,27 @@
         <v>1102</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D37" s="1">
         <v>335</v>
@@ -2296,24 +2296,24 @@
         <v>467</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="38" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D38" s="4">
         <v>438</v>
@@ -2322,24 +2322,24 @@
         <v>475</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="39" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D39" s="4">
         <v>15</v>
@@ -2348,24 +2348,24 @@
         <v>72</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="40" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D40" s="4">
         <v>17</v>
@@ -2374,24 +2374,24 @@
         <v>74</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D41" s="1">
         <v>489</v>
@@ -2400,24 +2400,24 @@
         <v>612</v>
       </c>
       <c r="F41" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H41" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D42" s="1">
         <v>282</v>
@@ -2426,24 +2426,24 @@
         <v>405</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="43" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D43" s="4">
         <v>65</v>
@@ -2452,24 +2452,24 @@
         <v>85</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D44" s="5">
         <v>13</v>
@@ -2478,24 +2478,24 @@
         <v>128</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="45" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D45" s="4">
         <v>1</v>
@@ -2504,24 +2504,24 @@
         <v>86</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D46" s="1">
         <v>295</v>
@@ -2530,24 +2530,24 @@
         <v>301</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="47" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D47" s="4">
         <v>309</v>
@@ -2556,24 +2556,24 @@
         <v>312</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D48" s="1">
         <v>296</v>
@@ -2582,24 +2582,24 @@
         <v>298</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="49" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D49" s="4">
         <v>1173</v>
@@ -2608,24 +2608,24 @@
         <v>1184</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D50" s="1">
         <v>564</v>
@@ -2634,24 +2634,24 @@
         <v>594</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D51" s="1">
         <v>611</v>
@@ -2660,24 +2660,24 @@
         <v>641</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D52" s="1">
         <v>539</v>
@@ -2686,47 +2686,47 @@
         <v>569</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="53" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D53" s="4">
         <v>88</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="54" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D54" s="4">
         <v>82</v>
@@ -2735,24 +2735,24 @@
         <v>82</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D55" s="1">
         <v>1042</v>
@@ -2761,24 +2761,24 @@
         <v>1056</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D56" s="1">
         <v>2502</v>
@@ -2787,24 +2787,24 @@
         <v>2608</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="57" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A57" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D57" s="5">
         <v>2038</v>
@@ -2813,24 +2813,24 @@
         <v>2055</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="58" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A58" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D58" s="5">
         <v>2157</v>
@@ -2839,24 +2839,24 @@
         <v>2174</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="59" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A59" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D59" s="5">
         <v>75</v>
@@ -2865,24 +2865,24 @@
         <v>75</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="60" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D60" s="4">
         <v>936</v>
@@ -2891,24 +2891,24 @@
         <v>1122</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="61" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A61" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D61" s="4">
         <v>358</v>
@@ -2917,24 +2917,24 @@
         <v>526</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="62" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D62" s="4">
         <v>3</v>
@@ -2943,24 +2943,24 @@
         <v>19</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="63" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D63" s="4">
         <v>1</v>
@@ -2969,47 +2969,47 @@
         <v>71</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D64" s="1">
         <v>318</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D65" s="1">
         <v>388</v>
@@ -3018,24 +3018,24 @@
         <v>540</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="66" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A66" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D66" s="4">
         <v>94</v>
@@ -3044,24 +3044,24 @@
         <v>211</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="67" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A67" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D67" s="4">
         <v>496</v>
@@ -3070,24 +3070,24 @@
         <v>648</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="68" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A68" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D68" s="4">
         <v>113</v>
@@ -3096,24 +3096,24 @@
         <v>230</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="69" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A69" s="9" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D69" s="9">
         <v>223</v>
@@ -3122,30 +3122,30 @@
         <v>249</v>
       </c>
       <c r="F69" s="9" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="I69" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="J69" s="9" t="s">
         <v>263</v>
-      </c>
-      <c r="J69" s="9" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="70" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A70" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D70" s="7">
         <v>502</v>
@@ -3154,27 +3154,27 @@
         <v>506</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H70" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="J70" s="7" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="71" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A71" s="6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D71" s="6">
         <v>535</v>
@@ -3183,24 +3183,24 @@
         <v>539</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G71" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="72" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A72" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D72" s="5">
         <v>227</v>
@@ -3209,24 +3209,24 @@
         <v>229</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="73" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A73" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D73" s="5">
         <v>351</v>
@@ -3235,24 +3235,24 @@
         <v>353</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H73" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="74" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A74" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D74" s="5">
         <v>350</v>
@@ -3261,24 +3261,24 @@
         <v>352</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H74" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="75" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A75" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D75" s="5">
         <v>416</v>
@@ -3287,24 +3287,24 @@
         <v>419</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H75" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D76" s="1">
         <v>426</v>
@@ -3313,24 +3313,24 @@
         <v>429</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D77" s="1">
         <v>230</v>
@@ -3339,24 +3339,24 @@
         <v>232</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="78" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A78" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D78" s="5">
         <v>351</v>
@@ -3365,24 +3365,24 @@
         <v>353</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H78" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="79" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A79" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D79" s="4">
         <v>391</v>
@@ -3391,24 +3391,24 @@
         <v>394</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D80" s="1">
         <v>298</v>
@@ -3417,24 +3417,24 @@
         <v>347</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="81" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A81" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D81" s="4">
         <v>191</v>
@@ -3443,24 +3443,24 @@
         <v>240</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D82" s="1">
         <v>102</v>
@@ -3469,24 +3469,24 @@
         <v>102</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D83" s="1">
         <v>53</v>
@@ -3495,24 +3495,24 @@
         <v>53</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D84" s="1">
         <v>114</v>
@@ -3521,24 +3521,24 @@
         <v>307</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="85" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A85" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D85" s="4">
         <v>115</v>
@@ -3547,24 +3547,24 @@
         <v>308</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H85" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="86" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A86" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D86" s="4">
         <v>125</v>
@@ -3573,24 +3573,24 @@
         <v>318</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="87" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A87" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D87" s="4">
         <v>117</v>
@@ -3599,24 +3599,24 @@
         <v>310</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="88" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A88" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D88" s="4">
         <v>119</v>
@@ -3625,24 +3625,24 @@
         <v>312</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H88" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="89" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A89" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D89" s="4">
         <v>46</v>
@@ -3651,27 +3651,27 @@
         <v>83</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J89" s="10" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="90" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A90" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D90" s="4">
         <v>583</v>
@@ -3680,24 +3680,24 @@
         <v>631</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="91" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A91" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D91" s="4">
         <v>579</v>
@@ -3706,24 +3706,24 @@
         <v>627</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="92" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A92" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D92" s="6">
         <v>88</v>
@@ -3732,27 +3732,27 @@
         <v>125</v>
       </c>
       <c r="F92" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I92" s="6" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="93" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A93" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D93" s="4">
         <v>301</v>
@@ -3761,24 +3761,24 @@
         <v>343</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="94" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A94" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D94" s="4">
         <v>35</v>
@@ -3787,24 +3787,24 @@
         <v>44</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H94" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D95" s="1">
         <v>309</v>
@@ -3813,24 +3813,24 @@
         <v>446</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="96" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A96" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D96" s="4">
         <v>1</v>
@@ -3839,24 +3839,24 @@
         <v>10</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H96" s="4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D97" s="1">
         <v>372</v>
@@ -3865,24 +3865,24 @@
         <v>519</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D98" s="1">
         <v>167</v>
@@ -3891,24 +3891,24 @@
         <v>297</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D99" s="1">
         <v>780</v>
@@ -3917,24 +3917,24 @@
         <v>822</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D100" s="1">
         <v>164</v>
@@ -3943,24 +3943,24 @@
         <v>185</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="101" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A101" s="5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D101" s="5">
         <v>176</v>
@@ -3969,24 +3969,24 @@
         <v>197</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G101" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H101" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="102" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A102" s="5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D102" s="5">
         <v>413</v>
@@ -3995,24 +3995,24 @@
         <v>434</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G102" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H102" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D103" s="1">
         <v>156</v>
@@ -4021,24 +4021,24 @@
         <v>177</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="104" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A104" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D104" s="4">
         <v>271</v>
@@ -4047,24 +4047,24 @@
         <v>278</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H104" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D105" s="1">
         <v>1</v>
@@ -4073,24 +4073,24 @@
         <v>83</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D106" s="1">
         <v>760</v>
@@ -4099,24 +4099,24 @@
         <v>765</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="107" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A107" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D107" s="4">
         <v>237</v>
@@ -4125,24 +4125,24 @@
         <v>271</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H107" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="108" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A108" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D108" s="4">
         <v>239</v>
@@ -4151,24 +4151,24 @@
         <v>273</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H108" s="4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D109" s="1">
         <v>1021</v>
@@ -4177,24 +4177,24 @@
         <v>1342</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D110" s="1">
         <v>793</v>
@@ -4203,24 +4203,24 @@
         <v>808</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="111" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A111" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D111" s="4">
         <v>1</v>
@@ -4229,24 +4229,24 @@
         <v>54</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H111" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D112" s="1">
         <v>422</v>
@@ -4255,24 +4255,24 @@
         <v>429</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D113" s="1">
         <v>815</v>
@@ -4281,24 +4281,24 @@
         <v>830</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D114" s="1">
         <v>92</v>
@@ -4307,24 +4307,24 @@
         <v>92</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="115" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A115" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D115" s="6">
         <v>142</v>
@@ -4333,24 +4333,24 @@
         <v>142</v>
       </c>
       <c r="F115" s="6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G115" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H115" s="6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="116" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A116" s="5" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D116" s="5">
         <v>127</v>
@@ -4359,24 +4359,24 @@
         <v>127</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G116" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H116" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="117" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A117" s="5" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D117" s="5">
         <v>82</v>
@@ -4385,24 +4385,24 @@
         <v>82</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G117" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H117" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="118" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A118" s="5" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D118" s="5">
         <v>77</v>
@@ -4411,24 +4411,24 @@
         <v>77</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G118" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H118" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="119" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A119" s="5" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D119" s="5">
         <v>126</v>
@@ -4437,24 +4437,24 @@
         <v>126</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G119" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H119" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D120" s="1">
         <v>3719</v>
@@ -4463,24 +4463,24 @@
         <v>3733</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="121" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A121" s="4" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D121" s="4">
         <v>151</v>
@@ -4489,24 +4489,24 @@
         <v>216</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H121" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="122" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A122" s="4" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D122" s="4">
         <v>132</v>
@@ -4515,24 +4515,24 @@
         <v>195</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H122" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="123" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A123" s="4" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D123" s="4">
         <v>154</v>
@@ -4541,24 +4541,24 @@
         <v>219</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H123" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="124" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A124" s="4" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D124" s="4">
         <v>114</v>
@@ -4567,24 +4567,24 @@
         <v>177</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G124" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H124" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="125" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A125" s="4" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D125" s="4">
         <v>161</v>
@@ -4593,24 +4593,24 @@
         <v>226</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H125" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="126" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A126" s="4" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D126" s="4">
         <v>170</v>
@@ -4619,24 +4619,24 @@
         <v>244</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H126" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="127" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A127" s="4" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D127" s="4">
         <v>528</v>
@@ -4645,24 +4645,24 @@
         <v>563</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H127" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="128" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A128" s="8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B128" s="8" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C128" s="8" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D128" s="8">
         <v>341</v>
@@ -4671,27 +4671,27 @@
         <v>523</v>
       </c>
       <c r="F128" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G128" s="8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H128" s="8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J128" s="8" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D129" s="1">
         <v>1049</v>
@@ -4700,13 +4700,13 @@
         <v>1091</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H129" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/Outputs_primates/AllGenes_Potential_CPDs.xlsx
+++ b/Outputs_primates/AllGenes_Potential_CPDs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adesinamary/Downloads/kondrashov/Outputs_primates/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uofh-my.sharepoint.com/personal/miadesin_cougarnet_uh_edu/Documents/Documents/Ricardo_lab/GitHub/kondrashov/Outputs_primates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DE7A887-EF3E-EB4A-B22C-4948E71FD544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{9DE7A887-EF3E-EB4A-B22C-4948E71FD544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F47388A-1A9F-4F9D-B719-C914BE634F54}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="23260" windowHeight="12460" xr2:uid="{BC6F7999-E049-F441-AF63-5F5D062E3B8F}"/>
+    <workbookView xWindow="-12" yWindow="0" windowWidth="11760" windowHeight="12336" xr2:uid="{BC6F7999-E049-F441-AF63-5F5D062E3B8F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -986,8 +986,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1323,17 +1323,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81CD1290-D98E-6145-998E-728A92BEC841}">
   <dimension ref="A1:J129"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.1640625" style="1"/>
-    <col min="2" max="2" width="18.83203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="11.19921875" style="1"/>
+    <col min="2" max="2" width="18.796875" style="1" customWidth="1"/>
     <col min="3" max="3" width="17" style="1" customWidth="1"/>
-    <col min="4" max="9" width="11.1640625" style="1"/>
-    <col min="10" max="10" width="55.33203125" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="11.1640625" style="1"/>
+    <col min="4" max="9" width="11.19921875" style="1"/>
+    <col min="10" max="10" width="55.296875" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="11.19921875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1365,7 +1365,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="J2" s="3"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1418,7 +1418,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -1444,7 +1444,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -1470,7 +1470,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>266</v>
       </c>
@@ -1496,7 +1496,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="7" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>14</v>
       </c>
@@ -1522,33 +1522,33 @@
         <v>273</v>
       </c>
     </row>
-    <row r="8" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="1">
         <v>286</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="1">
         <v>333</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>23</v>
       </c>
@@ -1574,7 +1574,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>23</v>
       </c>
@@ -1600,7 +1600,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>26</v>
       </c>
@@ -1626,7 +1626,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>26</v>
       </c>
@@ -1652,7 +1652,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>29</v>
       </c>
@@ -1678,7 +1678,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>29</v>
       </c>
@@ -1704,7 +1704,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>29</v>
       </c>
@@ -1730,7 +1730,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>37</v>
       </c>
@@ -1756,7 +1756,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>41</v>
       </c>
@@ -1782,7 +1782,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>41</v>
       </c>
@@ -1808,7 +1808,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>46</v>
       </c>
@@ -1834,7 +1834,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="20" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>46</v>
       </c>
@@ -1860,7 +1860,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>46</v>
       </c>
@@ -1886,7 +1886,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>46</v>
       </c>
@@ -1912,7 +1912,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>51</v>
       </c>
@@ -1938,7 +1938,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="24" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>51</v>
       </c>
@@ -1964,33 +1964,33 @@
         <v>54</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" s="1" t="s">
+    <row r="25" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="D25" s="1">
+      <c r="D25" s="4">
         <v>82</v>
       </c>
-      <c r="E25" s="1">
+      <c r="E25" s="4">
         <v>128</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="F25" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G25" s="1" t="s">
+      <c r="G25" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H25" s="1" t="s">
+      <c r="H25" s="4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="26" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>51</v>
       </c>
@@ -2016,7 +2016,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>51</v>
       </c>
@@ -2042,7 +2042,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>51</v>
       </c>
@@ -2068,7 +2068,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>56</v>
       </c>
@@ -2094,7 +2094,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="30" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>56</v>
       </c>
@@ -2120,7 +2120,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>56</v>
       </c>
@@ -2146,7 +2146,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="32" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>56</v>
       </c>
@@ -2172,7 +2172,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>62</v>
       </c>
@@ -2198,7 +2198,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="34" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>62</v>
       </c>
@@ -2224,7 +2224,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>62</v>
       </c>
@@ -2250,7 +2250,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
         <v>65</v>
       </c>
@@ -2279,7 +2279,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>65</v>
       </c>
@@ -2305,7 +2305,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="38" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>68</v>
       </c>
@@ -2331,7 +2331,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="39" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>71</v>
       </c>
@@ -2357,7 +2357,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="40" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>71</v>
       </c>
@@ -2383,7 +2383,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>74</v>
       </c>
@@ -2409,7 +2409,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>74</v>
       </c>
@@ -2435,7 +2435,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="43" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
         <v>77</v>
       </c>
@@ -2461,7 +2461,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="44" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
         <v>79</v>
       </c>
@@ -2487,7 +2487,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="45" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>79</v>
       </c>
@@ -2513,7 +2513,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>83</v>
       </c>
@@ -2539,7 +2539,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="47" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>85</v>
       </c>
@@ -2565,7 +2565,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>85</v>
       </c>
@@ -2591,7 +2591,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="49" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>88</v>
       </c>
@@ -2617,7 +2617,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>90</v>
       </c>
@@ -2643,7 +2643,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>90</v>
       </c>
@@ -2669,7 +2669,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>90</v>
       </c>
@@ -2695,7 +2695,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="53" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>96</v>
       </c>
@@ -2718,7 +2718,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="54" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
         <v>100</v>
       </c>
@@ -2744,7 +2744,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>102</v>
       </c>
@@ -2770,7 +2770,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>105</v>
       </c>
@@ -2796,7 +2796,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="57" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
         <v>107</v>
       </c>
@@ -2822,7 +2822,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="58" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
         <v>107</v>
       </c>
@@ -2848,7 +2848,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="59" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
         <v>110</v>
       </c>
@@ -2874,7 +2874,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="60" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
         <v>112</v>
       </c>
@@ -2900,7 +2900,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="61" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
         <v>112</v>
       </c>
@@ -2926,7 +2926,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="62" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
         <v>114</v>
       </c>
@@ -2952,7 +2952,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="63" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
         <v>117</v>
       </c>
@@ -2978,7 +2978,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>119</v>
       </c>
@@ -3001,7 +3001,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>119</v>
       </c>
@@ -3027,7 +3027,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="66" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
         <v>119</v>
       </c>
@@ -3053,7 +3053,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="67" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
         <v>119</v>
       </c>
@@ -3079,7 +3079,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="68" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
         <v>119</v>
       </c>
@@ -3105,7 +3105,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="69" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A69" s="9" t="s">
         <v>123</v>
       </c>
@@ -3137,7 +3137,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="70" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A70" s="7" t="s">
         <v>126</v>
       </c>
@@ -3166,7 +3166,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="71" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A71" s="6" t="s">
         <v>126</v>
       </c>
@@ -3192,7 +3192,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="72" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
         <v>126</v>
       </c>
@@ -3218,7 +3218,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="73" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
         <v>126</v>
       </c>
@@ -3244,7 +3244,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="74" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
         <v>126</v>
       </c>
@@ -3270,7 +3270,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="75" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
         <v>126</v>
       </c>
@@ -3296,7 +3296,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>126</v>
       </c>
@@ -3322,7 +3322,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>126</v>
       </c>
@@ -3348,7 +3348,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="78" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
         <v>126</v>
       </c>
@@ -3374,7 +3374,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="79" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
         <v>126</v>
       </c>
@@ -3400,7 +3400,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>128</v>
       </c>
@@ -3426,7 +3426,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="81" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
         <v>128</v>
       </c>
@@ -3452,7 +3452,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>131</v>
       </c>
@@ -3478,7 +3478,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>133</v>
       </c>
@@ -3504,7 +3504,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>135</v>
       </c>
@@ -3530,7 +3530,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="85" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="s">
         <v>135</v>
       </c>
@@ -3556,7 +3556,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="86" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
         <v>135</v>
       </c>
@@ -3582,7 +3582,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="87" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
         <v>135</v>
       </c>
@@ -3608,7 +3608,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="88" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A88" s="4" t="s">
         <v>135</v>
       </c>
@@ -3634,7 +3634,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="89" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
         <v>142</v>
       </c>
@@ -3663,7 +3663,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="90" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="s">
         <v>142</v>
       </c>
@@ -3689,7 +3689,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="91" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
         <v>142</v>
       </c>
@@ -3715,7 +3715,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="92" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A92" s="6" t="s">
         <v>142</v>
       </c>
@@ -3744,7 +3744,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="93" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
         <v>142</v>
       </c>
@@ -3770,7 +3770,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="94" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
         <v>145</v>
       </c>
@@ -3796,7 +3796,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
         <v>145</v>
       </c>
@@ -3822,7 +3822,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="96" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A96" s="4" t="s">
         <v>145</v>
       </c>
@@ -3848,7 +3848,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
         <v>150</v>
       </c>
@@ -3874,7 +3874,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
         <v>150</v>
       </c>
@@ -3900,7 +3900,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
         <v>153</v>
       </c>
@@ -3926,7 +3926,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
         <v>155</v>
       </c>
@@ -3952,7 +3952,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="101" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A101" s="5" t="s">
         <v>155</v>
       </c>
@@ -3978,7 +3978,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="102" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A102" s="5" t="s">
         <v>155</v>
       </c>
@@ -4004,7 +4004,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>155</v>
       </c>
@@ -4030,7 +4030,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="104" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A104" s="4" t="s">
         <v>158</v>
       </c>
@@ -4056,7 +4056,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
         <v>160</v>
       </c>
@@ -4082,7 +4082,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
         <v>163</v>
       </c>
@@ -4108,7 +4108,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="107" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
         <v>165</v>
       </c>
@@ -4134,7 +4134,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="108" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A108" s="4" t="s">
         <v>165</v>
       </c>
@@ -4160,7 +4160,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
         <v>168</v>
       </c>
@@ -4186,7 +4186,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
         <v>171</v>
       </c>
@@ -4212,7 +4212,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="111" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
         <v>173</v>
       </c>
@@ -4238,7 +4238,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
         <v>176</v>
       </c>
@@ -4264,7 +4264,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
         <v>179</v>
       </c>
@@ -4290,7 +4290,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
         <v>182</v>
       </c>
@@ -4316,7 +4316,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="115" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A115" s="6" t="s">
         <v>185</v>
       </c>
@@ -4342,7 +4342,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="116" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A116" s="5" t="s">
         <v>185</v>
       </c>
@@ -4368,7 +4368,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="117" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A117" s="5" t="s">
         <v>185</v>
       </c>
@@ -4394,7 +4394,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="118" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A118" s="5" t="s">
         <v>185</v>
       </c>
@@ -4420,7 +4420,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="119" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A119" s="5" t="s">
         <v>185</v>
       </c>
@@ -4446,7 +4446,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
         <v>187</v>
       </c>
@@ -4472,7 +4472,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="121" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A121" s="4" t="s">
         <v>189</v>
       </c>
@@ -4498,7 +4498,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="122" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A122" s="4" t="s">
         <v>189</v>
       </c>
@@ -4524,7 +4524,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="123" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A123" s="4" t="s">
         <v>189</v>
       </c>
@@ -4550,7 +4550,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="124" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A124" s="4" t="s">
         <v>189</v>
       </c>
@@ -4576,7 +4576,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="125" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A125" s="4" t="s">
         <v>189</v>
       </c>
@@ -4602,7 +4602,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="126" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A126" s="4" t="s">
         <v>189</v>
       </c>
@@ -4628,7 +4628,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="127" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A127" s="4" t="s">
         <v>191</v>
       </c>
@@ -4654,7 +4654,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="128" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A128" s="8" t="s">
         <v>193</v>
       </c>
@@ -4683,7 +4683,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
         <v>195</v>
       </c>

--- a/Outputs_primates/AllGenes_Potential_CPDs.xlsx
+++ b/Outputs_primates/AllGenes_Potential_CPDs.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{9DE7A887-EF3E-EB4A-B22C-4948E71FD544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F47388A-1A9F-4F9D-B719-C914BE634F54}"/>
   <bookViews>
-    <workbookView xWindow="-12" yWindow="0" windowWidth="11760" windowHeight="12336" xr2:uid="{BC6F7999-E049-F441-AF63-5F5D062E3B8F}"/>
+    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8880" xr2:uid="{BC6F7999-E049-F441-AF63-5F5D062E3B8F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
